--- a/docs/LumiaMed_verifica_commercialista.xlsx
+++ b/docs/LumiaMed_verifica_commercialista.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Casi di prova'!$A$1:$J$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parametri'!$A$1:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parametri'!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3. Foglio 'Parametri': confermi o corregga i parametri normativi 2026 usati dall'app.</t>
+          <t>3. Foglio 'Parametri': confermi o corregga i parametri normativi usati dall'app (in particolare quelli 'da verificare').</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Compie 30 anni il 15/3/2026: 3 mesi a 291,61 €/anno e 9 mesi a 566 €/anno, più maternità 95,54</t>
+          <t>Compie 30 anni il 15/3/2026: 3 mesi a 304,73 €/anno e 9 mesi a 591,47 €/anno, più maternità 84,26</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>592.9400000000001</v>
+        <v>604.05</v>
       </c>
       <c r="G34" s="8" t="n"/>
       <c r="H34" s="9" t="n"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Over 40 tutto l'anno: 1.961,56 + maternità 95,54</t>
+          <t>Over 40 tutto l'anno: 2.049,83 + maternità 84,26</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>2057.1</v>
+        <v>2134.09</v>
       </c>
       <c r="G35" s="8" t="n"/>
       <c r="H35" s="9" t="n"/>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Under 40, reddito forfettario (LM34) 31.200 €: 19,5% sulla parte oltre 5.446,77 €</t>
+          <t>Under 40, reddito forfettario (LM34) 31.200 €: 19,5% sulla parte oltre 5.691,90 € (soglia 2026 stimata)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>5446.77</v>
+        <v>5691.9</v>
       </c>
       <c r="G36" s="8" t="n"/>
       <c r="H36" s="9" t="n"/>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Under 40, reddito forfettario (LM34) 31.200 €: 19,5% sulla parte oltre 5.446,77 €</t>
+          <t>Under 40, reddito forfettario (LM34) 31.200 €: 19,5% sulla parte oltre 5.691,90 € (soglia 2026 stimata)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F37" s="7" t="n">
-        <v>5021.88</v>
+        <v>4974.08</v>
       </c>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="9" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Over 40, reddito 160.000 €: 19,5% fino a 150.000 (oltre la soglia di 10.059,28) + 1% sull'eccedenza</t>
+          <t>Over 40, reddito 160.000 €: 19,5% fino a 150.000 (oltre la soglia 2026 stimata di 10.511,95) + 1% sull'eccedenza</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F38" s="7" t="n">
-        <v>10059.28</v>
+        <v>10511.95</v>
       </c>
       <c r="G38" s="8" t="n"/>
       <c r="H38" s="9" t="n"/>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Over 40, reddito 160.000 €: 19,5% fino a 150.000 (oltre la soglia di 10.059,28) + 1% sull'eccedenza</t>
+          <t>Over 40, reddito 160.000 €: 19,5% fino a 150.000 (oltre la soglia 2026 stimata di 10.511,95) + 1% sull'eccedenza</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>27388.44</v>
+        <v>27300.17</v>
       </c>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="9" t="n"/>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="F40" s="7" t="n">
-        <v>5446.77</v>
+        <v>5691.9</v>
       </c>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="9" t="n"/>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.057,10 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
+          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.134,09 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.057,10 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
+          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.134,09 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>4352.79</v>
+        <v>4347.07</v>
       </c>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="9" t="n"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.057,10 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
+          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.134,09 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F53" s="7" t="n">
-        <v>4352.79</v>
+        <v>4347.07</v>
       </c>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="9" t="n"/>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.057,10 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
+          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.134,09 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.057,10 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
+          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.134,09 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="F55" s="7" t="n">
-        <v>5871.78</v>
+        <v>5828.01</v>
       </c>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="9" t="n"/>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.057,10 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
+          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.134,09 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.057,10 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
+          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.134,09 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="F57" s="7" t="n">
-        <v>10224.57</v>
+        <v>10175.08</v>
       </c>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="9" t="n"/>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.057,10 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
+          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.134,09 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.057,10 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
+          <t>Oggi 30/6/2026. Nato nel 1975, attività dal 2018, aliquota 15%. Incassi 7.500 € al mese da gennaio a giugno (45.000 €). Quota A 2026 versata il 30/4 (2.134,09 €). Anno 2025: imposta 9.000 €, acconti versati 7.000 €, ricavi 80.000 €, reddito 62.400 €. Quota A e B in unica soluzione.</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="F59" s="7" t="n">
-        <v>33755.33</v>
+        <v>33766.65</v>
       </c>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="9" t="n"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.057,10 €). Nessun dato dell'anno precedente.</t>
+          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.134,09 €). Nessun dato dell'anno precedente.</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.057,10 €). Nessun dato dell'anno precedente.</t>
+          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.134,09 €). Nessun dato dell'anno precedente.</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="F61" s="7" t="n">
-        <v>14185.14</v>
+        <v>14159.66</v>
       </c>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="9" t="n"/>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.057,10 €). Nessun dato dell'anno precedente.</t>
+          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.134,09 €). Nessun dato dell'anno precedente.</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="F62" s="7" t="n">
-        <v>3385.14</v>
+        <v>3359.66</v>
       </c>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="9" t="n"/>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.057,10 €). Nessun dato dell'anno precedente.</t>
+          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.134,09 €). Nessun dato dell'anno precedente.</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.057,10 €). Nessun dato dell'anno precedente.</t>
+          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.134,09 €). Nessun dato dell'anno precedente.</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="F64" s="7" t="n">
-        <v>7658.86</v>
+        <v>7592.84</v>
       </c>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="9" t="n"/>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.057,10 €). Nessun dato dell'anno precedente.</t>
+          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.134,09 €). Nessun dato dell'anno precedente.</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.057,10 €). Nessun dato dell'anno precedente.</t>
+          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.134,09 €). Nessun dato dell'anno precedente.</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="F66" s="7" t="n">
-        <v>11044</v>
+        <v>10952.5</v>
       </c>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="9" t="n"/>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.057,10 €). Nessun dato dell'anno precedente.</t>
+          <t>Oggi 30/9/2026. Ordinario, Sardegna (addizionale regionale 1,23%), comune non impostato. Nato nel 1975. Compensi 6.000 € al mese da strutture (gennaio-settembre, esenti IVA) con ritenuta di 1.200 € ciascuno. Affitto studio 800 € al mese. Quota A versata il 30/4 (2.134,09 €). Nessun dato dell'anno precedente.</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="F67" s="7" t="n">
-        <v>23417.4</v>
+        <v>23451.32</v>
       </c>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="9" t="n"/>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.157,66 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
+          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.194,18 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.157,66 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
+          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.194,18 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F69" s="7" t="n">
-        <v>1971.85</v>
+        <v>1970.11</v>
       </c>
       <c r="G69" s="8" t="n"/>
       <c r="H69" s="9" t="n"/>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.157,66 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
+          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.194,18 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.157,66 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
+          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.194,18 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.157,66 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
+          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.194,18 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F72" s="7" t="n">
-        <v>8110.44</v>
+        <v>8064.73</v>
       </c>
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="9" t="n"/>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.157,66 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
+          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.194,18 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.157,66 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
+          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.194,18 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="F74" s="7" t="n">
-        <v>8110.44</v>
+        <v>8064.73</v>
       </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="9" t="n"/>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.157,66 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
+          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.194,18 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.157,66 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
+          <t>Oggi 15/12/2026. Nato nel 1990, attività dal 2023 con requisiti per il 5%. Incassi 5.000 € al mese (60.000 €). Anno 2025: imposta 2.000 €, nessun acconto, ricavi 50.000 €, reddito 39.000 €. Versamenti senza indicazione: ENPAM 1.194,18 € il 30/4; F24 3.000 € il 20/7; ENPAM 6.542,88 € il 2/11; F24 1.000 € il 30/11.</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="F76" s="7" t="n">
-        <v>48810.8</v>
+        <v>48823.33</v>
       </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="9" t="n"/>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="F78" s="7" t="n">
-        <v>8949.860000000001</v>
+        <v>8932.98</v>
       </c>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="9" t="n"/>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F79" s="7" t="n">
-        <v>8949.860000000001</v>
+        <v>8932.98</v>
       </c>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="9" t="n"/>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="F80" s="7" t="n">
-        <v>2057.1</v>
+        <v>2134.09</v>
       </c>
       <c r="G80" s="8" t="n"/>
       <c r="H80" s="9" t="n"/>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="F81" s="7" t="n">
-        <v>4877.28</v>
+        <v>4833.51</v>
       </c>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="9" t="n"/>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="F83" s="7" t="n">
-        <v>18550.64</v>
+        <v>18566.98</v>
       </c>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="9" t="n"/>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="F84" s="7" t="n">
-        <v>15152.76</v>
+        <v>15175.24</v>
       </c>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="9" t="n"/>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="F88" s="7" t="n">
-        <v>2057.1</v>
+        <v>2134.09</v>
       </c>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="9" t="n"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="F89" s="7" t="n">
-        <v>1703.22</v>
+        <v>1690.89</v>
       </c>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="9" t="n"/>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="F91" s="7" t="n">
-        <v>5222.82</v>
+        <v>5287.48</v>
       </c>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="9" t="n"/>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="F93" s="7" t="n">
-        <v>9546.85</v>
+        <v>9548.42</v>
       </c>
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="9" t="n"/>
@@ -4239,7 +4239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4247,8 +4247,9 @@
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4279,10 +4280,15 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>Verificato</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
           <t>Confermato?</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Valore corretto / commento</t>
         </is>
@@ -4310,8 +4316,13 @@
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr"/>
-      <c r="F2" s="8" t="n"/>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4335,8 +4346,13 @@
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="8" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4360,8 +4376,13 @@
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="8" t="n"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4385,8 +4406,13 @@
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="8" t="n"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4410,58 +4436,81 @@
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="8" t="n"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>IRPEF 2026</t>
+          <t>Forfettario: redditi da lavoro dipendente</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Scaglione 1: 0 – 28.000,00 €</t>
+          <t>Soglia 2026 (redditi 2025)</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>35.000,00 €</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>L. 199/2025 (Legge di Bilancio 2026) art. 1 c. 3</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="8" t="n"/>
+          <t>L. 190/2014 art. 1 c. 57 lett. d-ter</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Da confermare dal commercialista.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>IRPEF 2026</t>
+          <t>Forfettario: redditi da lavoro dipendente</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Scaglione 2: 28.000,00 € – 50.000,00 €</t>
+          <t>Soglia 2027 provvisoria (redditi 2026)</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>30.000,00 €</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>L. 199/2025 (Legge di Bilancio 2026) art. 1 c. 3</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="8" t="n"/>
+          <t>L. 190/2014 art. 1 c. 57 lett. d-ter</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>da rivedere dopo la legge di bilancio 2027</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4471,12 +4520,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Scaglione 3: 50.000,00 € – oltre</t>
+          <t>Scaglione 1: 0 – 28.000,00 €</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -4485,58 +4534,73 @@
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="8" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Detrazione lavoro autonomo</t>
+          <t>IRPEF 2026</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Fino a 5.500,00 €</t>
+          <t>Scaglione 2: 28.000,00 € – 50.000,00 €</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>1.265,00 €</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Art. 13 c. 5 TUIR</t>
+          <t>L. 199/2025 (Legge di Bilancio 2026) art. 1 c. 3</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="8" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Detrazione lavoro autonomo</t>
+          <t>IRPEF 2026</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Da 5.500,00 € a 28.000,00 €</t>
+          <t>Scaglione 3: 50.000,00 € – oltre</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>500,00 € + 765,00 € × (28.000 − reddito) / 22.500</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Art. 13 c. 5 TUIR</t>
+          <t>L. 199/2025 (Legge di Bilancio 2026) art. 1 c. 3</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="8" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4546,12 +4610,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Da 28.000,00 € a 50.000,00 €</t>
+          <t>Fino a 5.500,00 €</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>500,00 € × (50.000 − reddito) / 22.000</t>
+          <t>1.265,00 €</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -4560,58 +4624,73 @@
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="8" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Acconti</t>
+          <t>Detrazione lavoro autonomo</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Nessun acconto sotto</t>
+          <t>Da 5.500,00 € a 28.000,00 €</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>51,65 €</t>
+          <t>500,00 € + 765,00 € × (28.000 − reddito) / 22.500</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Art. 17 DPR 435/2001; soggetti ISA e forfettari in due rate da 50%</t>
+          <t>Art. 13 c. 5 TUIR</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="8" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Acconti</t>
+          <t>Detrazione lavoro autonomo</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Unica soluzione (novembre) sotto</t>
+          <t>Da 28.000,00 € a 50.000,00 €</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>257,52 €</t>
+          <t>500,00 € × (50.000 − reddito) / 22.000</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Art. 17 DPR 435/2001; soggetti ISA e forfettari in due rate da 50%</t>
+          <t>Art. 13 c. 5 TUIR</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="8" t="n"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4621,12 +4700,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Percentuale acconto</t>
+          <t>Nessun acconto sotto</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51,65 €</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -4635,8 +4714,13 @@
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="8" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4646,12 +4730,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Prima rata soggetti ISA/forfettari</t>
+          <t>Unica soluzione (novembre) sotto</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>257,52 €</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -4660,8 +4744,13 @@
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="8" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4671,12 +4760,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Acconto addizionale comunale</t>
+          <t>Percentuale acconto</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -4685,566 +4774,697 @@
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="8" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>Acconti</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Quota A fino a 30 anni</t>
+          <t>Prima rata soggetti ISA/forfettari</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>291,61 €</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Importi Quota A 2026 discordanti tra le fonti (es. money.it riporta 304,73 / 591,47 / 1.109,92 / 2.049,83 e maternità 84,26). Verificare sul bollettino ENPAM.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n"/>
+          <t>Art. 17 DPR 435/2001; soggetti ISA e forfettari in due rate da 50%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>Acconti</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Quota A 30-35 anni</t>
+          <t>Acconto addizionale comunale</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>566,00 €</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
+          <t>Art. 17 DPR 435/2001; soggetti ISA e forfettari in due rate da 50%</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="8" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>ENPAM Quota A 2026</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Quota A 35-40 anni</t>
+          <t>Quota A fino a 30 anni</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>1.062,12 €</t>
+          <t>304,73 €</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="8" t="n"/>
+          <t>enpam.it</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>enpam.it agg. 19/3/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>ENPAM Quota A 2026</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Quota A da 40 anni</t>
+          <t>Quota A 30-35 anni</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>1.961,56 €</t>
+          <t>591,47 €</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
+          <t>enpam.it</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>ENPAM Quota A 2026</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Contributo maternità</t>
+          <t>Quota A 35-40 anni</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>95,54 €</t>
+          <t>1.109,92 €</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
+          <t>enpam.it</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>ENPAM Quota A 2026</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Quota B aliquota intera</t>
+          <t>Quota A da 40 anni</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>2.049,83 €</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
+          <t>enpam.it</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>ENPAM Quota A 2026</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Quota B massimale</t>
+          <t>Contributo maternità (si somma alla fascia)</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>150.000,00 €</t>
+          <t>84,26 €</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
+          <t>enpam.it</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>ENPAM Quota A 2026</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Quota B oltre massimale</t>
+          <t>Quota A studenti (non usata nei calcoli)</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>152,37 €</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
+          <t>enpam.it</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="n"/>
+      <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>ENPAM Quota B</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Soglia esente under 40</t>
+          <t>Quota B aliquota intera</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>5.446,77 €</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="8" t="n"/>
+          <t>Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Aliquote e massimale della Quota B da verificare.</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>ENPAM</t>
+          <t>ENPAM Quota B</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Soglia esente over 40</t>
+          <t>Quota B aliquota ridotta (a scelta del medico)</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>10.059,28 €</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Quota A: partitaiva.it / Fiscozen (2026); Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
+          <t>Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="8" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>IVA e bollo</t>
+          <t>ENPAM Quota B</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Bollo: soglia</t>
+          <t>Quota B massimale</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>77,47 €</t>
+          <t>150.000,00 €</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>DPR 642/72, tariffa art. 13</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>D.Lgs. 192/2024: dal 2025 i rimborsi di spese addebitate al cliente non concorrono al reddito di lavoro autonomo. Verificare se vale anche per il bollo e per i forfettari.</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n"/>
+          <t>Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>IVA e bollo</t>
+          <t>ENPAM Quota B</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Bollo: importo</t>
+          <t>Quota B oltre massimale</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>2,00 €</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>DPR 642/72, tariffa art. 13</t>
+          <t>Quota B: istruzioni Modello D 2026 (Giornale della Previdenza) e enpam.it</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="8" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>IVA e bollo</t>
+          <t>ENPAM soglie Quota B redditi 2025</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Bollo riaddebitato concorre al reddito</t>
+          <t>Soglia esente under 40</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>5.446,77 €</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>DPR 642/72, tariffa art. 13</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="8" t="n"/>
+          <t>enpam.it</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Redditi 2025, Quota B pagata nel 2026. enpam.it agg. 3/2/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
       <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>IVA e bollo</t>
+          <t>ENPAM soglie Quota B redditi 2025</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>IVA aliquota prestazioni non sanitarie</t>
+          <t>Soglia esente over 40</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>10.059,28 €</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>DPR 642/72, tariffa art. 13</t>
+          <t>enpam.it</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="8" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
       <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>IVA e bollo</t>
+          <t>ENPAM soglie Quota B redditi 2026</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Interessi liquidazione trimestrale</t>
+          <t>Soglia esente under 40</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>5.691,90 €</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>DPR 642/72, tariffa art. 13</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="8" t="n"/>
+          <t>Stima LumiaMed</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Stima: Quota A 2026 ÷ 19,5%. ENPAM la pubblica con il Modello D 2027</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Spese (ordinario)</t>
+          <t>ENPAM soglie Quota B redditi 2026</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità affitto_studio</t>
+          <t>Soglia esente over 40</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10.511,95 €</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
+          <t>Stima LumiaMed</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="8" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G33" s="8" t="n"/>
+      <c r="H33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Spese (ordinario)</t>
+          <t>Detrazione lavoro dipendente</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità utenze</t>
+          <t>Nulla oltre (solo per l'avviso sugli altri redditi)</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50.000,00 €</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="8" t="n"/>
+          <t>Art. 13 c. 1 TUIR</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Usata solo per l'avviso sugli altri redditi nell'ordinario: la detrazione per lavoro dipendente non è calcolata.</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Spese (ordinario)</t>
+          <t>IVA e bollo</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità materiale_sanitario</t>
+          <t>Bollo: soglia</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>77,47 €</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="8" t="n"/>
+          <t>DPR 642/72, tariffa art. 13</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>D.Lgs. 192/2024: dal 2025 i rimborsi di spese addebitate al cliente non concorrono al reddito di lavoro autonomo. Verificare se vale anche per il bollo e per i forfettari.</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G35" s="8" t="n"/>
+      <c r="H35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Spese (ordinario)</t>
+          <t>IVA e bollo</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità attrezzature</t>
+          <t>Bollo: importo</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2,00 €</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
+          <t>DPR 642/72, tariffa art. 13</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
-      <c r="F36" s="8" t="n"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Spese (ordinario)</t>
+          <t>IVA e bollo</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità assicurazione_rc</t>
+          <t>Bollo riaddebitato concorre al reddito</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
+          <t>DPR 642/72, tariffa art. 13</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="8" t="n"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Spese (ordinario)</t>
+          <t>IVA e bollo</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità formazione_ecm</t>
+          <t>IVA aliquota prestazioni non sanitarie</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
+          <t>DPR 642/72, tariffa art. 13</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr"/>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Spese (ordinario)</t>
+          <t>IVA e bollo</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità software</t>
+          <t>Interessi liquidazione trimestrale</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
+          <t>DPR 642/72, tariffa art. 13</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="8" t="n"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -5254,12 +5474,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità telefono_internet</t>
+          <t>Deducibilità affitto_studio</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -5268,8 +5488,13 @@
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
-      <c r="F40" s="8" t="n"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -5279,12 +5504,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità auto</t>
+          <t>Deducibilità utenze</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -5293,8 +5518,13 @@
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr"/>
-      <c r="F41" s="8" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -5304,12 +5534,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità ristoranti_alberghi</t>
+          <t>Deducibilità materiale_sanitario</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -5318,8 +5548,13 @@
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr"/>
-      <c r="F42" s="8" t="n"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -5329,7 +5564,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità commercialista</t>
+          <t>Deducibilità attrezzature</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
@@ -5343,8 +5578,13 @@
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr"/>
-      <c r="F43" s="8" t="n"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -5354,7 +5594,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità quota_ordine</t>
+          <t>Deducibilità assicurazione_rc</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
@@ -5368,8 +5608,13 @@
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr"/>
-      <c r="F44" s="8" t="n"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -5379,7 +5624,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità personale</t>
+          <t>Deducibilità formazione_ecm</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
@@ -5393,8 +5638,13 @@
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr"/>
-      <c r="F45" s="8" t="n"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -5404,12 +5654,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità contributi_enpam</t>
+          <t>Deducibilità software</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -5418,8 +5668,13 @@
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr"/>
-      <c r="F46" s="8" t="n"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G46" s="8" t="n"/>
+      <c r="H46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -5429,12 +5684,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità imposte_f24</t>
+          <t>Deducibilità telefono_internet</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -5443,8 +5698,13 @@
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr"/>
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -5454,12 +5714,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità personale_non_deducibile</t>
+          <t>Deducibilità auto</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -5468,8 +5728,13 @@
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -5479,12 +5744,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Deducibilità altro</t>
+          <t>Deducibilità ristoranti_alberghi</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -5493,143 +5758,383 @@
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Scadenze 2026</t>
+          <t>Spese (ordinario)</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Saldo e 1° acconto ISA/forfettari</t>
+          <t>Deducibilità commercialista</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Proroga ISA/forfettari 2026 al 20 luglio (edotto.com, centrofiscale.com); Modello D: istruzioni ENPAM 2026</t>
+          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Scadenze 2026</t>
+          <t>Spese (ordinario)</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>2° acconto</t>
+          <t>Deducibilità quota_ordine</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Proroga ISA/forfettari 2026 al 20 luglio (edotto.com, centrofiscale.com); Modello D: istruzioni ENPAM 2026</t>
+          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr"/>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Scadenze 2026</t>
+          <t>Spese (ordinario)</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Dichiarazione dei redditi</t>
+          <t>Deducibilità personale</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Proroga ISA/forfettari 2026 al 20 luglio (edotto.com, centrofiscale.com); Modello D: istruzioni ENPAM 2026</t>
+          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
-      <c r="F52" s="8" t="n"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Scadenze 2026</t>
+          <t>Spese (ordinario)</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Invio Sistema TS</t>
+          <t>Deducibilità contributi_enpam</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Proroga ISA/forfettari 2026 al 20 luglio (edotto.com, centrofiscale.com); Modello D: istruzioni ENPAM 2026</t>
+          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr"/>
-      <c r="F53" s="8" t="n"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
       <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
+          <t>Spese (ordinario)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Deducibilità imposte_f24</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Spese (ordinario)</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Deducibilità personale_non_deducibile</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Spese (ordinario)</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Deducibilità altro</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Art. 54 TUIR (prima della riforma D.Lgs. 192/2024: verificare le novità sul reddito di lavoro autonomo)</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
           <t>Scadenze 2026</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Saldo e 1° acconto ISA/forfettari</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Proroga ISA/forfettari 2026 al 20 luglio (edotto.com, centrofiscale.com); Modello D: istruzioni ENPAM 2026</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Scadenze 2026</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>2° acconto</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Proroga ISA/forfettari 2026 al 20 luglio (edotto.com, centrofiscale.com); Modello D: istruzioni ENPAM 2026</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="n"/>
+      <c r="H58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Scadenze 2026</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Dichiarazione dei redditi</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Proroga ISA/forfettari 2026 al 20 luglio (edotto.com, centrofiscale.com); Modello D: istruzioni ENPAM 2026</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Scadenze 2026</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Invio Sistema TS</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Proroga ISA/forfettari 2026 al 20 luglio (edotto.com, centrofiscale.com); Modello D: istruzioni ENPAM 2026</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Scadenze 2026</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Modello D ENPAM</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C61" s="18" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Proroga ISA/forfettari 2026 al 20 luglio (edotto.com, centrofiscale.com); Modello D: istruzioni ENPAM 2026</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
-  <conditionalFormatting sqref="A2:G54">
+  <autoFilter ref="A1:H61"/>
+  <conditionalFormatting sqref="A2:H61">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$F2="No"</formula>
+      <formula>$G2="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sì,No"</formula1>
     </dataValidation>
   </dataValidations>
